--- a/InputData/bldgs/DSCF/China-Distributed Solar Cap Factor.xlsx
+++ b/InputData/bldgs/DSCF/China-Distributed Solar Cap Factor.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhlx1\Desktop\eps-china2019-smart-trans\InputData\bldgs\DSCF\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
+    <workbookView windowWidth="24000" windowHeight="10845" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="4" r:id="rId1"/>
@@ -1565,11 +1570,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
-    <col min="2" max="2" width="73.4" customWidth="1"/>
-    <col min="3" max="3" width="15.0666666666667" customWidth="1"/>
-    <col min="4" max="4" width="13.3333333333333" customWidth="1"/>
+    <col min="2" max="2" width="73.3982300884956" customWidth="1"/>
+    <col min="3" max="3" width="15.070796460177" customWidth="1"/>
+    <col min="4" max="4" width="13.3362831858407" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1608,7 +1613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" ht="85.5" spans="1:2">
+    <row r="10" ht="83.25" spans="1:2">
       <c r="A10" s="37" t="s">
         <v>6</v>
       </c>
@@ -1681,9 +1686,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Y72"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
-    <col min="1" max="1" width="17.2666666666667" customWidth="1"/>
+    <col min="1" max="1" width="17.2654867256637" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -4751,10 +4756,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AT71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
-    <col min="1" max="1" width="17.2666666666667" style="3" customWidth="1"/>
-    <col min="2" max="2" width="8.46666666666667" style="3" customWidth="1"/>
+    <col min="1" max="1" width="17.2654867256637" style="3" customWidth="1"/>
+    <col min="2" max="2" width="8.46902654867257" style="3" customWidth="1"/>
     <col min="3" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -4818,7 +4823,7 @@
       <c r="AS1" s="6"/>
       <c r="AT1" s="6"/>
     </row>
-    <row r="2" spans="1:46">
+    <row r="2" ht="13.9" spans="1:46">
       <c r="A2" s="4"/>
       <c r="B2" s="9">
         <v>2010</v>
@@ -12058,8 +12063,14 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:AS2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
+  <dimension ref="A1:AS3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelRow="2"/>
+  <cols>
+    <col min="2" max="3" width="12.7964601769912"/>
+    <col min="4" max="4" width="10.5309734513274"/>
+    <col min="5" max="7" width="12.7964601769912"/>
+    <col min="9" max="22" width="12.7964601769912"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:45">
       <c r="B1">
@@ -12236,144 +12247,288 @@
         <v>0.110449991849099</v>
       </c>
       <c r="K2" s="1">
-        <f t="shared" ref="K2:R2" si="0">MIN(J2+0.005,1500/8760)</f>
+        <f>MIN(J2+0.005,1500/8760)</f>
         <v>0.115449991849099</v>
       </c>
       <c r="L2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="R2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="S2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="T2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="V2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="W2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="X2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AR2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>0.115449991849099</v>
+      </c>
+    </row>
+    <row r="3" spans="1:45">
+      <c r="B3">
+        <f>B2*8760</f>
+        <v>420.995079278294</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:L3" si="0">C2*8760</f>
+        <v>771.832106624229</v>
+      </c>
+      <c r="D3">
         <f t="shared" si="0"/>
-        <v>0.120449991849099</v>
-      </c>
-      <c r="M2" s="1">
+        <v>871.03526002254</v>
+      </c>
+      <c r="E3">
         <f t="shared" si="0"/>
-        <v>0.125449991849099</v>
-      </c>
-      <c r="N2" s="1">
+        <v>867.509901622588</v>
+      </c>
+      <c r="F3">
         <f t="shared" si="0"/>
-        <v>0.130449991849099</v>
-      </c>
-      <c r="O2" s="1">
+        <v>860.401086430777</v>
+      </c>
+      <c r="G3">
         <f t="shared" si="0"/>
-        <v>0.135449991849099</v>
-      </c>
-      <c r="P2" s="1">
+        <v>911.686334221546</v>
+      </c>
+      <c r="H3">
         <f t="shared" si="0"/>
-        <v>0.140449991849099</v>
-      </c>
-      <c r="Q2" s="1">
+        <v>818.273999952838</v>
+      </c>
+      <c r="I3">
         <f t="shared" si="0"/>
-        <v>0.145449991849099</v>
-      </c>
-      <c r="R2" s="1">
+        <v>923.741928598107</v>
+      </c>
+      <c r="J3">
         <f t="shared" si="0"/>
-        <v>0.150449991849099</v>
-      </c>
-      <c r="S2" s="1">
-        <f t="shared" ref="S2:AS2" si="1">MIN(R2+0.005,1500/8760)</f>
-        <v>0.155449991849099</v>
-      </c>
-      <c r="T2" s="1">
+        <v>967.541928598107</v>
+      </c>
+      <c r="K3">
+        <f t="shared" si="0"/>
+        <v>1011.34192859811</v>
+      </c>
+      <c r="L3">
+        <f t="shared" si="0"/>
+        <v>1011.34192859811</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:AS3" si="1">M2*8760</f>
+        <v>1011.34192859811</v>
+      </c>
+      <c r="N3">
         <f t="shared" si="1"/>
-        <v>0.160449991849099</v>
-      </c>
-      <c r="U2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="O3">
         <f t="shared" si="1"/>
-        <v>0.165449991849099</v>
-      </c>
-      <c r="V2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="P3">
         <f t="shared" si="1"/>
-        <v>0.170449991849099</v>
-      </c>
-      <c r="W2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="Q3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="X2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="R3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="Y2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="S3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="Z2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="T3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AA2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="U3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AB2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="V3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AC2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="W3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AD2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="X3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AE2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="Y3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AF2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="Z3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AG2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AA3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AH2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AB3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AI2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AC3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AJ2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AD3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AK2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AE3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AL2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AF3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AM2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AG3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AN2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AH3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AO2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AI3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AP2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AJ3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AQ2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AK3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AR2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AL3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
-      </c>
-      <c r="AS2" s="1">
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AM3">
         <f t="shared" si="1"/>
-        <v>0.171232876712329</v>
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>1011.34192859811</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>1011.34192859811</v>
       </c>
     </row>
   </sheetData>
